--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487502_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487502_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8447</v>
+        <v>5.6879</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3759</v>
+        <v>4.0853</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4689</v>
+        <v>1.6025</v>
       </c>
       <c r="G2" t="n">
         <v>2.9901</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1661</v>
+        <v>-0.323</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.387</v>
+        <v>-0.6775</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2209</v>
+        <v>0.3545</v>
       </c>
       <c r="V2" t="n">
         <v>2.4332</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4733</v>
+        <v>3.6074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6242</v>
+        <v>1.4435</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8491</v>
+        <v>2.1639</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.16</v>
+        <v>1.9338</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.866</v>
+        <v>2.8837</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.294</v>
+        <v>-0.9499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.641</v>
+        <v>2.1182</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2839</v>
+        <v>2.6744</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3571</v>
+        <v>-0.5562</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.801</v>
+        <v>-0.1844</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1499</v>
+        <v>0.2094</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6511</v>
+        <v>-0.3938</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>2.546</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9835</v>
+        <v>1.0238</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1206</v>
+        <v>0.4382</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1041</v>
+        <v>0.5856</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0415</v>
+        <v>1.8249</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0415</v>
+        <v>1.8249</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1119</v>
+        <v>2.8159</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9748</v>
+        <v>1.5309</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1371</v>
+        <v>1.2851</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9338</v>
+        <v>1.5449</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8837</v>
+        <v>2.424</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9499</v>
+        <v>-0.8791</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1182</v>
+        <v>2.6053</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6744</v>
+        <v>2.5552</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5562</v>
+        <v>0.0501</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1844</v>
+        <v>-1.0604</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2094</v>
+        <v>-0.1312</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3938</v>
+        <v>-0.9292</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
         <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5283</v>
+        <v>1.1916</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0306</v>
+        <v>0.6087</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5589</v>
+        <v>0.5828</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8249</v>
+        <v>0.2754</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8249</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0727</v>
+        <v>2.3495</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5738</v>
+        <v>0.436</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4989</v>
+        <v>1.9135</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5449</v>
+        <v>-1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>2.424</v>
+        <v>-0.866</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8791</v>
+        <v>-0.294</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6053</v>
+        <v>0.641</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5552</v>
+        <v>0.2839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0501</v>
+        <v>0.3571</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0604</v>
+        <v>-1.801</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1312</v>
+        <v>-1.1499</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9292</v>
+        <v>-0.6511</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4483</v>
+        <v>0.8597</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6516</v>
+        <v>-0.3088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7967</v>
+        <v>1.1685</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2754</v>
+        <v>3.0415</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2754</v>
+        <v>3.0415</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8483</v>
+        <v>2.1971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5913</v>
+        <v>0.7531</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2569</v>
+        <v>1.444</v>
       </c>
       <c r="G6" t="n">
         <v>1.8593</v>
@@ -922,13 +922,13 @@
         <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3232</v>
+        <v>-0.9744</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7128</v>
+        <v>-0.5511</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4233</v>
       </c>
       <c r="V6" t="n">
         <v>0.3329</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.6955</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.1895</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9652</v>
+        <v>1.885</v>
       </c>
       <c r="G7" t="n">
         <v>0.477</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0646</v>
+        <v>0.6309</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6534</v>
+        <v>0.1223</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5888</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8192</v>
+        <v>1.4842</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4712</v>
+        <v>-0.2072</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2904</v>
+        <v>1.6914</v>
       </c>
       <c r="G8" t="n">
         <v>1.2406</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7923</v>
+        <v>-1.1273</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9504</v>
+        <v>-0.6864</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8419</v>
+        <v>-0.4409</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8082</v>
+        <v>0.9062</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4703</v>
+        <v>-0.3276</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6621</v>
+        <v>1.2338</v>
       </c>
       <c r="G9" t="n">
-        <v>1.042</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6274</v>
+        <v>-0.0323</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4145</v>
+        <v>-0.0556</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8409</v>
+        <v>-0.4993</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0326</v>
+        <v>0.1021</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8083</v>
+        <v>-0.6014</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.799</v>
+        <v>0.4114</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4052</v>
+        <v>-0.1344</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3938</v>
+        <v>0.5458</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2363</v>
+        <v>0.2107</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2537</v>
+        <v>0.1717</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0175</v>
+        <v>0.039</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8825</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7608</v>
+        <v>0.3781</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1188</v>
+        <v>-0.5281</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8796</v>
+        <v>0.9063</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.101</v>
+        <v>-0.4836</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5634</v>
+        <v>0.1541</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6644</v>
+        <v>-0.6377</v>
       </c>
       <c r="V10" t="n">
         <v>0.6659</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>R. REGUERA SOUTO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3097</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7369</v>
+        <v>0.0429</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0467</v>
+        <v>0.0446</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.6822</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0323</v>
+        <v>0.4093</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0556</v>
+        <v>0.2729</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4993</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1021</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4114</v>
+        <v>0.6822</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1344</v>
+        <v>0.4093</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5458</v>
+        <v>0.2729</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3858</v>
+        <v>-0.5948</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2376</v>
+        <v>0.0429</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1482</v>
+        <v>-0.6377</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. REGUERA SOUTO</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0416</v>
+        <v>-0.0234</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0594</v>
+        <v>0.3446</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0178</v>
+        <v>-0.368</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6822</v>
+        <v>1.042</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4093</v>
+        <v>0.6274</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2729</v>
+        <v>0.4145</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.8409</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.0326</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.8083</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6822</v>
+        <v>-0.799</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4093</v>
+        <v>-0.4052</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2729</v>
+        <v>-0.3938</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7238</v>
+        <v>1.4046</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0594</v>
+        <v>1.128</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6644</v>
+        <v>0.2766</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.8825</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7374</v>
+        <v>-1.3221</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1567</v>
+        <v>-2.688</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4193</v>
+        <v>1.3659</v>
       </c>
       <c r="G13" t="n">
         <v>0.6596</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2219</v>
+        <v>-0.8066</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1286</v>
+        <v>-0.6599</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1467</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.2698</v>
+        <v>19.8638</v>
       </c>
       <c r="E14" t="n">
-        <v>4.102099999999999</v>
+        <v>4.6959</v>
       </c>
       <c r="F14" t="n">
-        <v>15.1678</v>
+        <v>15.168</v>
       </c>
       <c r="G14" t="n">
         <v>11.1816</v>
@@ -1534,10 +1534,10 @@
         <v>-2.3332</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1557000000000002</v>
+        <v>0.1556999999999997</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9790999999999999</v>
+        <v>0.9791000000000003</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6885</v>
@@ -1546,13 +1546,13 @@
         <v>15.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4177</v>
+        <v>1.0116</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8117000000000005</v>
+        <v>-0.2178000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2293</v>
+        <v>1.229299999999999</v>
       </c>
       <c r="V14" t="n">
         <v>6.6913</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0559</v>
+        <v>0.7477</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5333</v>
+        <v>-0.6947</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5226</v>
+        <v>1.4425</v>
       </c>
       <c r="G15" t="n">
         <v>0.0803</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7798</v>
+        <v>0.4715</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8138</v>
+        <v>0.5858</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.034</v>
+        <v>-0.1142</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1856</v>
+        <v>0.4822</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0216</v>
+        <v>0.6123</v>
       </c>
       <c r="F16" t="n">
-        <v>0.164</v>
+        <v>-0.1301</v>
       </c>
       <c r="G16" t="n">
         <v>-2.7076</v>
@@ -1702,13 +1702,13 @@
         <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>0.178</v>
+        <v>-0.5254</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2988</v>
+        <v>-0.7081</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4768</v>
+        <v>0.1828</v>
       </c>
       <c r="V16" t="n">
         <v>0.9733000000000001</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.498</v>
+        <v>-0.3873</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9878</v>
+        <v>-0.4762</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4898</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.9675</v>
@@ -1780,13 +1780,13 @@
         <v>2.7419</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1903</v>
+        <v>0.301</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9457</v>
+        <v>-0.4341</v>
       </c>
       <c r="U17" t="n">
-        <v>1.136</v>
+        <v>0.735</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4599</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7413</v>
+        <v>-1.2342</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6236</v>
+        <v>-2.0096</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8823</v>
+        <v>0.7753</v>
       </c>
       <c r="G18" t="n">
         <v>0.3125</v>
@@ -1858,13 +1858,13 @@
         <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0858</v>
+        <v>-0.5787</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6633</v>
+        <v>-1.0492</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5774</v>
+        <v>0.4705</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5763</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0875</v>
+        <v>-1.7316</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9138</v>
+        <v>-1.5045</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1737</v>
+        <v>-0.2271</v>
       </c>
       <c r="G19" t="n">
         <v>-2.23</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2491</v>
+        <v>0.1067</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0353</v>
+        <v>0.4446</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2844</v>
+        <v>-0.3379</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4267</v>
+        <v>-3.3908</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3012</v>
+        <v>-2.5059</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1255</v>
+        <v>-0.8849</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9601</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1892</v>
+        <v>0.2251</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0306</v>
+        <v>-0.2353</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2198</v>
+        <v>0.4604</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4599</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0953</v>
+        <v>-3.4989</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.0911</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5948</v>
+        <v>-3.4077</v>
       </c>
       <c r="G21" t="n">
         <v>1.1958</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4869</v>
+        <v>0.1095</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2023</v>
+        <v>0.207</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2846</v>
+        <v>-0.0975</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0415</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3309</v>
+        <v>-4.5844</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7743</v>
+        <v>-4.0813</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5566</v>
+        <v>-0.5031</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9328</v>
@@ -2170,13 +2170,13 @@
         <v>1.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3438</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8057</v>
+        <v>0.4987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4619</v>
+        <v>-0.4085</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3317</v>
+        <v>-5.6726</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6215</v>
+        <v>-4.4169</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7101</v>
+        <v>-1.2557</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9072</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2768</v>
+        <v>-0.6177</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5387</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5334</v>
+        <v>-0.079</v>
       </c>
       <c r="V23" t="n">
         <v>-1.127</v>
@@ -2284,10 +2284,10 @@
         <v>-19.2699</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.1678</v>
+        <v>-15.1679</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.102</v>
+        <v>-4.101900000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-11.1816</v>
@@ -2326,13 +2326,13 @@
         <v>14.6886</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4174999999999999</v>
+        <v>-0.4177000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-1.2293</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8117000000000002</v>
+        <v>0.8116000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-6.6913</v>
